--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +492 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +567 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +567 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +492 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +492 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +473 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
+          <t>Décote lisible : des travaux sont signalés dans l'annonce.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +473 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +456 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
+++ b/docs/dossiers/dossier-paris-10e-bdc8acf7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
